--- a/#BBNaija_anonymized.xlsx
+++ b/#BBNaija_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -991,7 +991,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2177,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2904,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4269,7 +4269,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5346,7 +5346,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6275,7 +6275,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6443,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6958,7 +6958,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7213,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7588,7 +7588,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7629,7 +7629,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7791,7 +7791,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8176,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8265,7 +8265,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8732,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9364,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9451,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9538,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9580,7 +9580,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9748,7 +9748,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9832,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10087,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10130,7 +10130,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10172,7 +10172,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10299,7 +10299,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10343,7 +10343,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10478,7 +10478,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10688,7 +10688,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11156,7 +11156,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11243,7 +11243,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11330,7 +11330,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11595,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11724,7 +11724,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11766,7 +11766,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11810,7 +11810,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11895,7 +11895,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11937,7 +11937,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11979,7 +11979,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12021,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12151,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12235,7 +12235,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12277,7 +12277,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12403,7 +12403,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12493,7 +12493,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12714,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12757,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12843,7 +12843,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12971,7 +12971,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13143,7 +13143,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13353,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13523,7 +13523,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13565,7 +13565,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13612,7 +13612,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13654,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13740,7 +13740,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13782,7 +13782,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13953,7 +13953,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14041,7 +14041,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14128,7 +14128,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14257,7 +14257,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14426,7 +14426,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14468,7 +14468,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14552,7 +14552,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14810,7 +14810,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15049,7 +15049,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15136,7 +15136,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15178,7 +15178,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15305,7 +15305,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15347,7 +15347,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15476,7 +15476,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15561,7 +15561,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15604,7 +15604,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15774,7 +15774,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15818,7 +15818,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15862,7 +15862,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16124,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16168,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16254,7 +16254,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16296,7 +16296,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16426,7 +16426,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16640,7 +16640,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16773,7 +16773,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16817,7 +16817,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16865,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16911,7 +16911,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17000,7 +17000,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17175,7 +17175,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17302,7 +17302,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17349,7 +17349,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17648,7 +17648,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17690,7 +17690,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17774,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17858,7 +17858,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17900,7 +17900,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18027,7 +18027,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18069,7 +18069,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18154,7 +18154,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18245,7 +18245,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18287,7 +18287,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18329,7 +18329,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18371,7 +18371,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18455,7 +18455,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18497,7 +18497,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18540,7 +18540,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18582,7 +18582,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18668,7 +18668,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18837,7 +18837,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18921,7 +18921,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18999,7 +18999,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19045,7 +19045,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19090,7 +19090,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19133,7 +19133,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19261,7 +19261,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19305,7 +19305,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19347,7 +19347,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19433,7 +19433,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19475,7 +19475,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19519,7 +19519,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19561,7 +19561,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19647,7 +19647,7 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19689,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19859,7 +19859,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20078,7 +20078,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20120,7 +20120,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20162,7 +20162,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20206,7 +20206,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20291,7 +20291,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20335,7 +20335,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20420,7 +20420,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20462,7 +20462,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20505,7 +20505,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20547,7 +20547,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20590,7 +20590,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20632,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20674,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20718,7 +20718,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20760,7 +20760,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20803,7 +20803,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20845,7 +20845,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20887,7 +20887,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20972,7 +20972,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21056,7 +21056,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21098,7 +21098,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21142,7 +21142,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21230,7 +21230,7 @@
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21445,7 +21445,7 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21578,7 +21578,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21621,7 +21621,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21664,7 +21664,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21710,7 +21710,7 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21798,7 +21798,7 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21842,7 +21842,7 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21886,7 +21886,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21972,7 +21972,7 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22017,7 +22017,7 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22060,7 +22060,7 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22149,7 +22149,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22192,7 +22192,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22237,7 +22237,7 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22281,7 +22281,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22325,7 +22325,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22368,7 +22368,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22411,7 +22411,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22453,7 +22453,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22497,7 +22497,7 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22540,7 +22540,7 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22582,7 +22582,7 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22624,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22668,7 +22668,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22798,7 +22798,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22841,7 +22841,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22890,7 +22890,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22933,7 +22933,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22975,7 +22975,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23103,7 +23103,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23145,7 +23145,7 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23188,7 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23317,7 +23317,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23360,7 +23360,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23402,7 +23402,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23446,7 +23446,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23489,7 +23489,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23531,7 +23531,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23574,7 +23574,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23659,7 +23659,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23745,7 +23745,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23784,7 +23784,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23822,7 +23822,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23860,7 +23860,7 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23937,7 +23937,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23975,7 +23975,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24019,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24096,7 +24096,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24181,7 +24181,7 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24224,7 +24224,7 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24267,7 +24267,7 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24310,7 +24310,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24397,7 +24397,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24440,7 +24440,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24483,7 +24483,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24526,7 +24526,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24569,7 +24569,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24612,7 +24612,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24656,7 +24656,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24747,7 +24747,7 @@
       </c>
       <c r="J569" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24789,7 +24789,7 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24837,7 +24837,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24879,7 +24879,7 @@
       </c>
       <c r="J572" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24922,7 +24922,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25006,7 +25006,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25052,7 +25052,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25139,7 +25139,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25183,7 +25183,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25225,7 +25225,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25267,7 +25267,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25310,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25354,7 +25354,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25404,7 +25404,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25579,7 +25579,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25676,7 +25676,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25725,7 +25725,7 @@
       </c>
       <c r="J591" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25805,7 +25805,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25844,7 +25844,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25922,7 +25922,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25961,7 +25961,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26000,7 +26000,7 @@
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
